--- a/data/raw/gercekler.xlsx
+++ b/data/raw/gercekler.xlsx
@@ -1,40 +1,401 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sinan\OneDrive - Erzurum Teknik Üniversitesi\kızılelmaproject\kizilelmAI\data\raw\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53680EE-B414-423B-9DBB-42F617A9E569}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="115">
+  <si>
+    <t>Haber Metni</t>
+  </si>
+  <si>
+    <t>Cumhurbaşkanı Erdoğan, kabine toplantısının ardından açıklamalarda bulundu.</t>
+  </si>
+  <si>
+    <t>Türkiye'nin ilk yerli otomobili Togg, satış rekorları kırmaya devam ediyor.</t>
+  </si>
+  <si>
+    <t>Meteoroloji Genel Müdürlüğü, Marmara Bölgesi için sağanak yağış uyarısı yaptı.</t>
+  </si>
+  <si>
+    <t>Milli Eğitim Bakanlığı, okulların açılacağı tarihi resmi olarak duyurdu.</t>
+  </si>
+  <si>
+    <t>Teknofest Havacılık, Uzay ve Teknoloji Festivali bu yıl İzmir'de düzenlenecek.</t>
+  </si>
+  <si>
+    <t>Sağlık Bakanı, grip vakalarındaki artışa dikkat çekerek aşı uyarısında bulundu.</t>
+  </si>
+  <si>
+    <t>Erzurum Teknik Üniversitesi öğrencileri yapay zeka projesiyle ödül aldı.</t>
+  </si>
+  <si>
+    <t>Türkiye Cumhuriyet Merkez Bankası faiz kararını yarın açıklayacak.</t>
+  </si>
+  <si>
+    <t>İstanbul'da trafik yoğunluğu sabah saatlerinde yüzde 70 seviyesine ulaştı.</t>
+  </si>
+  <si>
+    <t>Milli sporcumuz, Avrupa Şampiyonası'nda altın madalya kazandı.</t>
+  </si>
+  <si>
+    <t>Japonya'da faaliyet gösteren maglev trenleri, mıknatıslar yardımıyla raylara değmeden saatte 600 kilometre hıza ulaşabilmektedir.</t>
+  </si>
+  <si>
+    <t>Güneş Sistemi'ndeki en büyük gezegen olan Jüpiter, o kadar büyüktür ki diğer tüm gezegenlerin toplam kütlesinden daha ağırdır.</t>
+  </si>
+  <si>
+    <t>Mustafa Kemal Atatürk, 19 Mayıs 1919'da Samsun'a çıkarak Milli Mücadele'yi başlatmış ve Türk milletinin bağımsızlık savaşının meşalesini yakmıştır.</t>
+  </si>
+  <si>
+    <t>Türkiye Cumhuriyeti Merkez Bankası, ülkenin para politikasını yönetmek ve fiyat istikrarını sağlamakla görevli bağımsız bir kurumdur.</t>
+  </si>
+  <si>
+    <t>Antibiyotikler, bakteriyel enfeksiyonları tedavi etmekte kullanılır, ancak virüslere karşı (örneğin grip veya soğuk algınlığı) herhangi bir etkisi yoktur.</t>
+  </si>
+  <si>
+    <t>Antibiyotikler, bakteriyel enfeksiyonları tedavi etmekte kullanılır, ancak virüslere karşı herhangi bir etkisi yoktur.</t>
+  </si>
+  <si>
+    <t>İnsan DNA'sının yaklaşık %99.9'u tüm insanlarda aynıdır, bizi farklı kılan şey o kalan binde birlik kısımdır.</t>
+  </si>
+  <si>
+    <t>Mona Lisa tablosu, Leonardo da Vinci tarafından 16. yüzyılda resmedilmiş ve şu anda Paris'teki Louvre Müzesi'nde sergilenmektedir.</t>
+  </si>
+  <si>
+    <t>Ay'a ilk ayak basan insan, 1969 yılındaki Apollo 11 göreviyle ABD'li astronot Neil Armstrong olmuştur.</t>
+  </si>
+  <si>
+    <t>Suyun kaynama noktası deniz seviyesinde 100 derece iken, yükseklere çıkıldıkça atmosferik basıncın düşmesi nedeniyle su daha düşük sıcaklıklarda kaynar.</t>
+  </si>
+  <si>
+    <t>Çita, karada yaşayan hayvanlar arasında en hızlı koşan canlıdır ve saatte 120 kilometre hıza ulaşabilir.</t>
+  </si>
+  <si>
+    <t>Türkiye'nin en yüksek dağı, 5.137 metre yüksekliğiyle Ağrı Dağı'dır.</t>
+  </si>
+  <si>
+    <t>Dünyanın en uzun nehri olan Nil Nehri, Afrika kıtasında yer alır ve Akdeniz'e dökülür.</t>
+  </si>
+  <si>
+    <t>Albert Einstein, 1921 yılında fotoelektrik etki üzerine yaptığı çalışmalar nedeniyle Nobel Fizik Ödülü'ne layık görülmüştür.</t>
+  </si>
+  <si>
+    <t>Kara delikler, kütle çekimleri o kadar güçlü olan astronomik cisimlerdir ki ışık dahi onlardan kaçamaz.</t>
+  </si>
+  <si>
+    <t>Penguenler uçamayan kuşlar olmakla birlikte mükemmel yüzücülerdir ve genellikle Güney Yarımküre'de yaşarlar.</t>
+  </si>
+  <si>
+    <t>Güneş Sistemi'mize en yakın yıldız sistemi Alfa Centauri'dir.</t>
+  </si>
+  <si>
+    <t>İnsan kalbi, günde ortalama 100.000 kez atarak tüm vücuda oksijen bakımından zengin kan pompalar.</t>
+  </si>
+  <si>
+    <t>Bakteriler, antibiyotiklerin bilinçsiz kullanımı sonucunda direnç kazanarak antibiyotiklerin etkisiz hale gelmesine neden olabilir.</t>
+  </si>
+  <si>
+    <t>Roma İmparatorluğu'nun başkenti olan Roma, İtalya sınırları içerisinde yer alan tarihi bir şehirdir.</t>
+  </si>
+  <si>
+    <t>Oksijen, insan vücudunda enerji üretimi için hayati öneme sahip olan bir gazdır.</t>
+  </si>
+  <si>
+    <t>Zebraların üzerindeki siyah ve beyaz çizgiler, sinekleri uzak tutmak ve kamuflaj sağlamak amacıyla evrimleşmiştir.</t>
+  </si>
+  <si>
+    <t>Satürn gezegeni, çevresindeki buz ve kaya parçalarından oluşan muhteşem halka sistemi ile bilinir.</t>
+  </si>
+  <si>
+    <t>Kutup ayıları, Kuzey Kutbu çevresindeki deniz buzullarında yaşayan devasa etçil yırtıcılardır.</t>
+  </si>
+  <si>
+    <t>Edison, ampulü tek başına icat etmemiş, ancak ticari olarak kullanılabilecek ilk pratik karbon flamanlı ampulü geliştirmiştir.</t>
+  </si>
+  <si>
+    <t>Mısır Piramitleri, antik Mısır firavunlarına anıt mezar olarak devasa taş bloklarla inşa edilmiştir.</t>
+  </si>
+  <si>
+    <t>Kuşların kemikleri, ağırlıklarını hafifletip uçmalarını kolaylaştırmak için içi boş peteksi bir yapıya sahiptir.</t>
+  </si>
+  <si>
+    <t>Amazon Ormanları, Dünya'nın akciğerleri olarak bilinir ve gezegenimizdeki oksijenin önemli bir kısmını üretir.</t>
+  </si>
+  <si>
+    <t>Depremler, yer kabuğunu oluşturan tektonik plakaların ani hareketleri sonucu ortaya çıkan sarsıntılardır.</t>
+  </si>
+  <si>
+    <t>C vitamini eksikliği, iskorbüt (skorbüt) adı verilen, diş etlerinde kanama ve halsizlikle kendini gösteren bir hastalığa yol açar.</t>
+  </si>
+  <si>
+    <t>Büyük Patlama (Big Bang) teorisine göre evren, yaklaşık 13.8 milyar yıl önce tek bir noktadan genişlemeye başlamıştır.</t>
+  </si>
+  <si>
+    <t>Köpeklerin koku alma duyusu, insanlarınkinden binlerce kat daha güçlüdür.</t>
+  </si>
+  <si>
+    <t>Titanik gemisi, 1912 yılındaki ilk seferinde bir buzdağına çarparak Kuzey Atlantik Okyanusu'nda batmıştır.</t>
+  </si>
+  <si>
+    <t>Yaz mevsimi, Kuzey Yarımküre'de Güneş ışınlarının yeryüzüne daha dik bir açıyla geldiği aylarda yaşanır.</t>
+  </si>
+  <si>
+    <t>Dünya, kendi ekseni etrafında batıdan doğuya doğru döndüğü için Güneş doğuda doğar ve batıda batar.</t>
+  </si>
+  <si>
+    <t>Müslümanların kutsal kitabı Kur'an-ı Kerim, Hz. Muhammed'e vahiy yoluyla indirilmiştir.</t>
+  </si>
+  <si>
+    <t>Kangurular, sadece Avustralya kıtasına özgü keseli memelilerdir.</t>
+  </si>
+  <si>
+    <t>Samanyolu Galaksisi, Güneş sistemimizin de içinde bulunduğu devasa sarmal bir galaksidir.</t>
+  </si>
+  <si>
+    <t>Mavi balinalar, yeryüzünde yaşamış olduğu bilinen en büyük hayvan türüdür.</t>
+  </si>
+  <si>
+    <t>Birleşmiş Milletler (BM), II. Dünya Savaşı sonrasında dünya barışını ve güvenliğini sağlamak amacıyla kurulmuştur.</t>
+  </si>
+  <si>
+    <t>Kuvars kristalleri, saatlerin zamanı şaşmadan doğru göstermesi için piezoelektrik özelliklerinden faydalanılarak kullanılır.</t>
+  </si>
+  <si>
+    <t>Osmanlı İmparatorluğu, 1453 yılında Fatih Sultan Mehmed önderliğinde İstanbul'u fethederek Bizans'a son vermiştir.</t>
+  </si>
+  <si>
+    <t>Elmas, karbon atomlarının çok yüksek basınç ve sıcaklık altında kristalleşmesiyle oluşan en sert doğal maddedir.</t>
+  </si>
+  <si>
+    <t>Kızılderililer, Kristof Kolomb'un Amerika kıtasına gelmesinden asırlar önce bu topraklarda yaşayan yerli halklardır.</t>
+  </si>
+  <si>
+    <t>Platon, Antik Yunan felsefesinin en büyük düşünürlerinden ve Aristoteles'in hocasıdır.</t>
+  </si>
+  <si>
+    <t>Venüs gezegeni, Güneş Sistemi'ndeki en sıcak gezegendir çünkü sera etkisi yaratan sülfürik asit dolu yoğun bir atmosfere sahiptir.</t>
+  </si>
+  <si>
+    <t>Mikroskop, gözle görülemeyecek kadar küçük canlıları ve yapıları incelemek için mercek sistemleri kullanan bir cihazdır.</t>
+  </si>
+  <si>
+    <t>Kaktüsler, suyu gövdelerinde depolayarak çöl gibi kurak ve zorlu iklim koşullarında hayatta kalabilen dikenli bitkilerdir.</t>
+  </si>
+  <si>
+    <t>Dünyanın en derin noktası, Büyük Okyanus'ta bulunan ve 11 kilometre derinliğe sahip Mariana Çukuru'dur.</t>
+  </si>
+  <si>
+    <t>Kanın kırmızı rengi, içinde bulunan ve oksijen taşımakla görevli hemoglobin adlı demir içeren proteinden gelir.</t>
+  </si>
+  <si>
+    <t>Japon kültüründe samuraylar, kendilerine has katı ahlak ve onur kodları olan (Bushido) eski dönem savaşçı sınıfıdır.</t>
+  </si>
+  <si>
+    <t>  Japonya'da faaliyet gösteren maglev trenleri, mıknatıslar yardımıyla raylara değmeden saatte 600 kilometre hıza ulaşabilmektedir.,</t>
+  </si>
+  <si>
+    <t>        Güneş Sistemi'ndeki en büyük gezegen olan Jüpiter, o kadar büyüktür ki diğer tüm gezegenlerin toplam kütlesinden daha ağırdır.,</t>
+  </si>
+  <si>
+    <t>        Mustafa Kemal Atatürk, 19 Mayıs 1919'da Samsun'a çıkarak Milli Mücadele'yi başlatmış ve Türk milletinin bağımsızlık savaşının meşalesini yakmıştır.,</t>
+  </si>
+  <si>
+    <t>        Türkiye Cumhuriyeti Merkez Bankası, ülkenin para politikasını yönetmek ve fiyat istikrarını sağlamakla görevli bağımsız bir kurumdur.,</t>
+  </si>
+  <si>
+    <t>        Antibiyotikler, bakteriyel enfeksiyonları tedavi etmekte kullanılır, ancak virüslere karşı herhangi bir etkisi yoktur.,</t>
+  </si>
+  <si>
+    <t>        İnsan DNA'sının yaklaşık %99.9'u tüm insanlarda aynıdır, bizi farklı kılan şey o kalan binde birlik kısımdır.,</t>
+  </si>
+  <si>
+    <t>        Mona Lisa tablosu, Leonardo da Vinci tarafından 16. yüzyılda resmedilmiş ve şu anda Paris'teki Louvre Müzesi'nde sergilenmektedir.,</t>
+  </si>
+  <si>
+    <t>        Ay'a ilk ayak basan insan, 1969 yılındaki Apollo 11 göreviyle ABD'li astronot Neil Armstrong olmuştur.,</t>
+  </si>
+  <si>
+    <t>        Suyun kaynama noktası deniz seviyesinde 100 derece iken, yükseklere çıkıldıkça atmosferik basıncın düşmesi nedeniyle su daha düşük sıcaklıklarda kaynar.,</t>
+  </si>
+  <si>
+    <t>        Çita, karada yaşayan hayvanlar arasında en hızlı koşan canlıdır ve saatte 120 kilometre hıza ulaşabilir.,</t>
+  </si>
+  <si>
+    <t>        Türkiye'nin en yüksek dağı, 5.137 metre yüksekliğiyle Ağrı Dağı'dır.,</t>
+  </si>
+  <si>
+    <t>        Dünyanın en uzun nehri olan Nil Nehri, Afrika kıtasında yer alır ve Akdeniz'e dökülür.,</t>
+  </si>
+  <si>
+    <t>        Albert Einstein, 1921 yılında fotoelektrik etki üzerine yaptığı çalışmalar nedeniyle Nobel Fizik Ödülü'ne layık görülmüştür.,</t>
+  </si>
+  <si>
+    <t>        Kara delikler, kütle çekimleri o kadar güçlü olan astronomik cisimlerdir ki ışık dahi onlardan kaçamaz.,</t>
+  </si>
+  <si>
+    <t>        Penguenler uçamayan kuşlar olmakla birlikte mükemmel yüzücülerdir ve genellikle Güney Yarımküre'de yaşarlar.,</t>
+  </si>
+  <si>
+    <t>        Güneş Sistemi'mize en yakın yıldız sistemi Alfa Centauri'dir.,</t>
+  </si>
+  <si>
+    <t>        İnsan kalbi, günde ortalama 100.000 kez atarak tüm vücuda oksijen bakımından zengin kan pompalar.,</t>
+  </si>
+  <si>
+    <t>        Bakteriler, antibiyotiklerin bilinçsiz kullanımı sonucunda direnç kazanarak antibiyotiklerin etkisiz hale gelmesine neden olabilir.,</t>
+  </si>
+  <si>
+    <t>        Roma İmparatorluğu'nun başkenti olan Roma, İtalya sınırları içerisinde yer alan tarihi bir şehirdir.,</t>
+  </si>
+  <si>
+    <t>        Oksijen, insan vücudunda enerji üretimi için hayati öneme sahip olan bir gazdır.,</t>
+  </si>
+  <si>
+    <t>        Zebraların üzerindeki siyah ve beyaz çizgiler, sinekleri uzak tutmak ve kamuflaj sağlamak amacıyla evrimleşmiştir.,</t>
+  </si>
+  <si>
+    <t>        Satürn gezegeni, çevresindeki buz ve kaya parçalarından oluşan muhteşem halka sistemi ile bilinir.,</t>
+  </si>
+  <si>
+    <t>        Kutup ayıları, Kuzey Kutbu çevresindeki deniz buzullarında yaşayan devasa etçil yırtıcılardır.,</t>
+  </si>
+  <si>
+    <t>        Edison, ampulü tek başına icat etmemiş, ancak ticari olarak kullanılabilecek ilk pratik karbon flamanlı ampulü geliştirmiştir.,</t>
+  </si>
+  <si>
+    <t>        Mısır Piramitleri, antik Mısır firavunlarına anıt mezar olarak devasa taş bloklarla inşa edilmiştir.,</t>
+  </si>
+  <si>
+    <t>        Kuşların kemikleri, ağırlıklarını hafifletip uçmalarını kolaylaştırmak için içi boş peteksi bir yapıya sahiptir.,</t>
+  </si>
+  <si>
+    <t>        Amazon Ormanları, Dünya'nın akciğerleri olarak bilinir ve gezegenimizdeki oksijenin önemli bir kısmını üretir.,</t>
+  </si>
+  <si>
+    <t>        Depremler, yer kabuğunu oluşturan tektonik plakaların ani hareketleri sonucu ortaya çıkan sarsıntılardır.,</t>
+  </si>
+  <si>
+    <t>        C vitamini eksikliği, iskorbüt (skorbüt) adı verilen, diş etlerinde kanama ve halsizlikle kendini gösteren bir hastalığa yol açar.,</t>
+  </si>
+  <si>
+    <t>        Büyük Patlama (Big Bang) teorisine göre evren, yaklaşık 13.8 milyar yıl önce tek bir noktadan genişlemeye başlamıştır.,</t>
+  </si>
+  <si>
+    <t>        Köpeklerin koku alma duyusu, insanlarınkinden binlerce kat daha güçlüdür.,</t>
+  </si>
+  <si>
+    <t>        Titanik gemisi, 1912 yılındaki ilk seferinde bir buzdağına çarparak Kuzey Atlantik Okyanusu'nda batmıştır.,</t>
+  </si>
+  <si>
+    <t>        Yaz mevsimi, Kuzey Yarımküre'de Güneş ışınlarının yeryüzüne daha dik bir açıyla geldiği aylarda yaşanır.,</t>
+  </si>
+  <si>
+    <t>        Dünya, kendi ekseni etrafında batıdan doğuya doğru döndüğü için Güneş doğuda doğar ve batıda batar.,</t>
+  </si>
+  <si>
+    <t>        Müslümanların kutsal kitabı Kur'an-ı Kerim, Hz. Muhammed'e vahiy yoluyla indirilmiştir.,</t>
+  </si>
+  <si>
+    <t>        Kangurular, sadece Avustralya kıtasına özgü keseli memelilerdir.,</t>
+  </si>
+  <si>
+    <t>        Samanyolu Galaksisi, Güneş sistemimizin de içinde bulunduğu devasa sarmal bir galaksidir.,</t>
+  </si>
+  <si>
+    <t>        Mavi balinalar, yeryüzünde yaşamış olduğu bilinen en büyük hayvan türüdür.,</t>
+  </si>
+  <si>
+    <t>        Birleşmiş Milletler (BM), II. Dünya Savaşı sonrasında dünya barışını ve güvenliğini sağlamak amacıyla kurulmuştur.,</t>
+  </si>
+  <si>
+    <t>        Kuvars kristalleri, saatlerin zamanı şaşmadan doğru göstermesi için piezoelektrik özelliklerinden faydalanılarak kullanılır.,</t>
+  </si>
+  <si>
+    <t>        Osmanlı İmparatorluğu, 1453 yılında Fatih Sultan Mehmed önderliğinde İstanbul'u fethederek Bizans'a son vermiştir.,</t>
+  </si>
+  <si>
+    <t>        Elmas, karbon atomlarının çok yüksek basınç ve sıcaklık altında kristalleşmesiyle oluşan en sert doğal maddedir.,</t>
+  </si>
+  <si>
+    <t>        Kızılderililer, Kristof Kolomb'un Amerika kıtasına gelmesinden asırlar önce bu topraklarda yaşayan yerli halklardır.,</t>
+  </si>
+  <si>
+    <t>        Platon, Antik Yunan felsefesinin en büyük düşünürlerinden ve Aristoteles'in hocasıdır.,</t>
+  </si>
+  <si>
+    <t>        Venüs gezegeni, Güneş Sistemi'ndeki en sıcak gezegendir çünkü sera etkisi yaratan sülfürik asit dolu yoğun bir atmosfere sahiptir.,</t>
+  </si>
+  <si>
+    <t>        Mikroskop, gözle görülemeyecek kadar küçük canlıları ve yapıları incelemek için mercek sistemleri kullanan bir cihazdır.,</t>
+  </si>
+  <si>
+    <t>        Kaktüsler, suyu gövdelerinde depolayarak çöl gibi kurak ve zorlu iklim koşullarında hayatta kalabilen dikenli bitkilerdir.,</t>
+  </si>
+  <si>
+    <t>        Dünyanın en derin noktası, Büyük Okyanus'ta bulunan ve 11 kilometre derinliğe sahip Mariana Çukuru'dur.,</t>
+  </si>
+  <si>
+    <t>        Kanın kırmızı rengi, içinde bulunan ve oksijen taşımakla görevli hemoglobin adlı demir içeren proteinden gelir.,</t>
+  </si>
+  <si>
+    <t>        Japon kültüründe samuraylar, kendilerine has katı ahlak ve onur kodları olan (Bushido) eski dönem savaşçı sınıfıdır.,</t>
+  </si>
+  <si>
+    <t>        Gökkuşağı, güneş ışığının yağmur damlalarının içinden geçerken kırılarak renklere ayrılmasıyla oluşan bir doğa olayıdır.,</t>
+  </si>
+  <si>
+    <t>        DNA molekülü, çift sarmal yapıda olup adenin, timin, guanin ve sitozin adı verilen dört temel nükleotitten oluşur.,</t>
+  </si>
+  <si>
+    <t>        Mars gezegeni, yüzeyindeki yoğun demir oksit (pas) maddesi sebebiyle kızılımsı bir görünüme sahiptir.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +403,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,89 +728,603 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A119"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Haber Metni</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Cumhurbaşkanı Erdoğan, kabine toplantısının ardından açıklamalarda bulundu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Türkiye'nin ilk yerli otomobili Togg, satış rekorları kırmaya devam ediyor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Meteoroloji Genel Müdürlüğü, Marmara Bölgesi için sağanak yağış uyarısı yaptı.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Milli Eğitim Bakanlığı, okulların açılacağı tarihi resmi olarak duyurdu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Teknofest Havacılık, Uzay ve Teknoloji Festivali bu yıl İzmir'de düzenlenecek.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Sağlık Bakanı, grip vakalarındaki artışa dikkat çekerek aşı uyarısında bulundu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Erzurum Teknik Üniversitesi öğrencileri yapay zeka projesiyle ödül aldı.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Türkiye Cumhuriyet Merkez Bankası faiz kararını yarın açıklayacak.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>İstanbul'da trafik yoğunluğu sabah saatlerinde yüzde 70 seviyesine ulaştı.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Milli sporcumuz, Avrupa Şampiyonası'nda altın madalya kazandı.</t>
-        </is>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
